--- a/data/trans_bre/P19-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 15,49</t>
+          <t>1,72; 15,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 10,06</t>
+          <t>-5,28; 9,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 14,18</t>
+          <t>0,03; 13,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 14,94</t>
+          <t>2,73; 14,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 54,11</t>
+          <t>4,52; 52,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 32,04</t>
+          <t>-13,65; 30,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 44,95</t>
+          <t>-0,06; 43,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 45,21</t>
+          <t>6,83; 41,9</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,7</t>
+          <t>2,18; 16,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 15,14</t>
+          <t>-0,27; 15,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 17,47</t>
+          <t>2,74; 16,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 18,08</t>
+          <t>6,02; 18,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 58,01</t>
+          <t>6,45; 59,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 51,09</t>
+          <t>-0,65; 52,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 60,35</t>
+          <t>7,19; 56,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,39; 67,37</t>
+          <t>17,96; 71,89</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 13,44</t>
+          <t>-2,0; 13,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 22,14</t>
+          <t>7,83; 22,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 16,3</t>
+          <t>-0,35; 16,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 27,51</t>
+          <t>-2,16; 28,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 60,65</t>
+          <t>-7,75; 60,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,3; 114,88</t>
+          <t>33,42; 115,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 68,91</t>
+          <t>-1,73; 68,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 381,25</t>
+          <t>-7,33; 307,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 14,33</t>
+          <t>5,34; 13,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 13,3</t>
+          <t>4,79; 12,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,3</t>
+          <t>5,09; 13,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 15,06</t>
+          <t>-6,96; 14,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 70,18</t>
+          <t>22,15; 68,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,68; 77,52</t>
+          <t>23,49; 73,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 54,94</t>
+          <t>18,09; 54,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 70,37</t>
+          <t>-28,38; 69,28</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 17,1</t>
+          <t>5,87; 17,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,97</t>
+          <t>3,28; 12,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 11,51</t>
+          <t>1,92; 11,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 15,02</t>
+          <t>-2,41; 13,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 110,68</t>
+          <t>26,55; 109,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,17; 72,68</t>
+          <t>13,61; 73,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 52,41</t>
+          <t>7,56; 51,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 85,47</t>
+          <t>-12,05; 81,16</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,08</t>
+          <t>-3,25; 8,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -0,4</t>
+          <t>-13,88; -0,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -3,68</t>
+          <t>-16,55; -3,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 0,45</t>
+          <t>-20,35; 1,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 40,26</t>
+          <t>-11,52; 40,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,27; -1,33</t>
+          <t>-35,39; -1,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,91; -9,97</t>
+          <t>-35,92; -9,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 2,47</t>
+          <t>-48,91; 5,54</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,88</t>
+          <t>4,32; 8,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,77</t>
+          <t>3,75; 8,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,73</t>
+          <t>3,42; 7,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 10,18</t>
+          <t>-0,32; 10,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,07; 37,02</t>
+          <t>16,74; 36,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,76; 33,11</t>
+          <t>14,2; 34,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 27,73</t>
+          <t>11,53; 28,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 47,63</t>
+          <t>-0,24; 47,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,66</t>
+          <t>1,39; 15,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 9,75</t>
+          <t>-5,03; 10,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 13,74</t>
+          <t>0,01; 14,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,21</t>
+          <t>1,89; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 52,18</t>
+          <t>4,64; 56,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 30,81</t>
+          <t>-12,79; 32,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 43,25</t>
+          <t>0,01; 45,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 41,9</t>
+          <t>4,37; 40,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,89</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 16,21</t>
+          <t>1,31; 15,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,32</t>
+          <t>0,13; 14,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 16,52</t>
+          <t>2,29; 17,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,6</t>
+          <t>6,65; 18,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 59,9</t>
+          <t>4,85; 59,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 52,34</t>
+          <t>-0,43; 50,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 56,6</t>
+          <t>6,68; 62,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 71,89</t>
+          <t>19,83; 70,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,91</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 13,72</t>
+          <t>-1,15; 15,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 22,25</t>
+          <t>8,14; 22,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 16,7</t>
+          <t>-0,35; 17,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 28,28</t>
+          <t>-5,93; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 60,42</t>
+          <t>-4,2; 67,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,42; 115,4</t>
+          <t>33,98; 112,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 68,79</t>
+          <t>-0,99; 67,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 307,99</t>
+          <t>-18,32; 32,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>57,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,88</t>
+          <t>5,54; 14,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,77</t>
+          <t>4,92; 12,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 13,38</t>
+          <t>4,91; 13,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 14,86</t>
+          <t>8,46; 16,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 68,07</t>
+          <t>22,88; 67,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 73,7</t>
+          <t>22,85; 74,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,09; 54,49</t>
+          <t>17,65; 54,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 69,28</t>
+          <t>34,82; 81,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 17,57</t>
+          <t>6,24; 17,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,9</t>
+          <t>3,25; 13,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,31</t>
+          <t>1,73; 11,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 13,84</t>
+          <t>1,78; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,55; 109,83</t>
+          <t>29,16; 111,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,61; 73,41</t>
+          <t>14,5; 74,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 51,63</t>
+          <t>6,51; 54,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 81,16</t>
+          <t>8,83; 76,98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-8,98</t>
+          <t>-8,06</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-28,5%</t>
+          <t>-26,28%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 8,12</t>
+          <t>-3,0; 7,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -0,66</t>
+          <t>-13,4; -1,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -3,52</t>
+          <t>-16,12; -3,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 1,24</t>
+          <t>-18,97; 1,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 40,92</t>
+          <t>-10,35; 42,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,39; -1,86</t>
+          <t>-34,77; -4,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,92; -9,21</t>
+          <t>-35,7; -9,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 5,54</t>
+          <t>-47,72; 6,78</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,72</t>
+          <t>4,18; 8,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,08</t>
+          <t>3,69; 7,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,93</t>
+          <t>3,3; 7,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 10,57</t>
+          <t>2,71; 7,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,74; 36,81</t>
+          <t>15,89; 36,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 34,43</t>
+          <t>14,3; 33,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,53; 28,31</t>
+          <t>10,92; 27,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 47,31</t>
+          <t>9,73; 28,38</t>
         </is>
       </c>
     </row>
